--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
@@ -9,7 +9,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoSCoW_эксперт 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_коллектив" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_расчеты" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_итоги" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +45,10 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,9 +195,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -588,12 +614,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -644,7 +670,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -661,17 +687,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -688,12 +714,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -715,7 +741,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -732,7 +758,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -749,12 +775,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -771,7 +797,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -781,7 +807,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -798,12 +824,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -815,17 +841,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -842,12 +868,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -867,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -919,12 +945,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -970,12 +996,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -992,17 +1018,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1045,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1067,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1089,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1080,7 +1106,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1102,17 +1128,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1155,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1172,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1199,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1245,12 +1271,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1301,12 +1327,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1323,17 +1349,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1371,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1403,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -1389,17 +1415,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1437,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1443,7 +1469,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1455,17 +1481,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1503,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1525,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -1529,1593 +1555,2680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Пример применения MoSCoW_четкая модель коллективного принятия решений</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Таблица 1_Удельные веса оценок экспертов для расчета итоговой взвешенной средней оценки</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Перечень экспертов</t>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F142"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Четкий MoSCoW — расчеты (коллективное решение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Веса экспертов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Эксперт</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ненормализованные весовые коэффициенты для принятия решения экспертами</t>
+          <t>Вес_raw</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Нормализованные весовые коэффициенты для принятия решения экспертами</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+          <t>Вес_norm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Итого</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 2_Индивидуальные экспертные рейтинги функциональных задач по MoSCoW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C8" s="18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2) Параметры алгоритма</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>beta (параметр консенсуса)</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>3) Индивидуальные экспертные рейтинги функциональных задач по MoSCoW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="C12" t="n">
-        <v>12.425</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11.625</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B16" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>6.600000000000001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.775</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B17" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>15.095</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B18" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>7.095000000000001</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="C15" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B19" s="14" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>18.78</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="C16" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9.125</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B20" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6.600000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B21" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>8.91</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="C18" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B22" s="14" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>10.78</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="C19" t="n">
-        <v>12.425</v>
-      </c>
-      <c r="D19" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B23" s="14" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="C20" t="n">
-        <v>13.275</v>
-      </c>
-      <c r="D20" t="n">
-        <v>9.125</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1.815</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>8.275</v>
-      </c>
-      <c r="C21" t="n">
-        <v>13.275</v>
-      </c>
-      <c r="D21" t="n">
-        <v>10.775</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Коэфициент Бета</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Матрицы согласия (AM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="B25" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>14.27</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>4) Матрицы согласия (AM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.8780918727915195</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.8215547703180212</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="n">
-        <v>0.8780918727915195</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.9356136820925552</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="n">
-        <v>0.8215547703180212</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.9356136820925552</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="13" t="inlineStr"/>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0.9837037037037037</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.8797615104339186</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>0.9837037037037037</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>0.8943358728055647</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>0.8797615104339186</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0.8943358728055647</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.8534482758620691</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="n">
-        <v>0.6285714285714286</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.7365079365079364</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="n">
-        <v>0.8534482758620691</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.7365079365079364</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="13" t="inlineStr"/>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>0.7751937984496123</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>0.7751937984496123</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1"/>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.8829787234042554</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.6646586345381525</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="n">
-        <v>0.8829787234042554</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.5868794326241135</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="n">
-        <v>0.6646586345381525</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.5868794326241135</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="13" t="inlineStr"/>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>0.9897674418604652</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>0.8825187969924813</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>0.9897674418604652</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>0.8734883720930233</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>0.8825187969924813</v>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>0.8734883720930233</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.8488372093023255</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="n">
-        <v>0.8488372093023255</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.5793650793650794</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="13" t="inlineStr"/>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>0.9302325581395349</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>0.9836065573770493</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>0.9302325581395349</v>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.945736434108527</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>0.9836065573770493</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>0.945736434108527</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.7659574468085107</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="n">
-        <v>0.7659574468085107</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.4680851063829788</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.4680851063829788</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="13" t="inlineStr"/>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C62" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.7659574468085107</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.7662037037037037</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>0.7659574468085107</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.5868794326241135</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>0.7662037037037037</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.5868794326241135</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="13" t="inlineStr"/>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+      <c r="C69" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.997991967871486</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.8674698795180724</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>0.997991967871486</v>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.869215291750503</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="n">
-        <v>0.8674698795180724</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.869215291750503</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="13" t="inlineStr"/>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="14" t="n">
+        <v>0.9863013698630135</v>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>0.9863013698630135</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>0.9863013698630135</v>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>0.9863013698630135</v>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1"/>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.8097928436911488</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.8488372093023255</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="n">
-        <v>0.8097928436911488</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.687382297551789</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="n">
-        <v>0.8488372093023255</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.687382297551789</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="13" t="inlineStr"/>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1"/>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.623352165725047</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.7679814385150812</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="n">
-        <v>0.623352165725047</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.8116760828625236</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="n">
-        <v>0.7679814385150812</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.8116760828625236</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 3_ Средняя степень согласия эксперта (Ai)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="13" t="inlineStr"/>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>0.9306236860546603</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>0.9306236860546603</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>0.9306236860546603</v>
+      </c>
+      <c r="C86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="n">
+        <v>0.9306236860546603</v>
+      </c>
+      <c r="C87" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>5) Средняя степень согласия эксперта A(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="13" t="inlineStr">
         <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0.8498233215547704</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.9068527774420374</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.8785842262052882</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="B91" s="14" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>0.9479166666666667</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>0.9479166666666667</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0.8375</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.7875000000000001</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="B92" s="14" t="n">
+        <v>0.9317326070688112</v>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>0.9390197882546343</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>0.8870486916197416</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0.7410098522167488</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.6825396825396826</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0.7949781061850028</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="B93" s="14" t="n">
+        <v>0.8520930232558139</v>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>0.7596899224806202</v>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>0.8675968992248062</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0.773818678971204</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.7349290780141844</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.625769033581133</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="B94" s="14" t="n">
+        <v>0.9361431194264732</v>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>0.9316279069767442</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>0.8780035845427523</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0.765688445921004</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.6309523809523809</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.7141011443337024</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="B95" s="14" t="n">
+        <v>0.9569195577582921</v>
+      </c>
+      <c r="C95" s="14" t="n">
+        <v>0.9379844961240309</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>0.9646714957427882</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.688534278959811</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.6170212765957448</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.5395981087470449</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="B96" s="14" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C96" s="14" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0.7660805752561073</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.6764184397163121</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.6765415681639086</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="B97" s="14" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>0.9897959183673469</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>0.9897959183673469</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0.9327309236947792</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.9336036298109945</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.8683425856342877</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="B98" s="14" t="n">
+        <v>0.9863013698630135</v>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>0.9931506849315068</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>0.9931506849315068</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0.8293150264967372</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.7485875706214689</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.7681097534270573</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="B99" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0.695666802120064</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.7175141242937852</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.7898287606888024</v>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 4_ Относительная степень согласия эксперта (RADi)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="B100" s="14" t="n">
+        <v>0.9306236860546603</v>
+      </c>
+      <c r="C100" s="14" t="n">
+        <v>0.9653118430273302</v>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>0.9653118430273302</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1"/>
+    <row r="102" ht="20" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>6) Относительная степень согласия эксперта RAD(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
         <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>0.3224817348887906</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.3441226541337967</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.3333956109774127</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="B105" s="14" t="n">
+        <v>0.3208955223880597</v>
+      </c>
+      <c r="C105" s="14" t="n">
+        <v>0.3395522388059701</v>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>0.3395522388059701</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>0.3526315789473684</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.3315789473684211</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="B106" s="14" t="n">
+        <v>0.3378534483433561</v>
+      </c>
+      <c r="C106" s="14" t="n">
+        <v>0.3404958365925754</v>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>0.3216507150640686</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>0.3340097452661445</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.3076543514463702</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0.3583359032874854</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="B107" s="14" t="n">
+        <v>0.343671835917959</v>
+      </c>
+      <c r="C107" s="14" t="n">
+        <v>0.3064032016008004</v>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>0.3499249624812406</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0.3625263958527237</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.3443070025320003</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0.2931666016152761</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="B108" s="14" t="n">
+        <v>0.3409395351295621</v>
+      </c>
+      <c r="C108" s="14" t="n">
+        <v>0.3392951130303377</v>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>0.3197653518401002</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0.362757957327737</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.2989244491080798</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0.3383175935641833</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="B109" s="14" t="n">
+        <v>0.3346369211625633</v>
+      </c>
+      <c r="C109" s="14" t="n">
+        <v>0.3280152875299973</v>
+      </c>
+      <c r="D109" s="14" t="n">
+        <v>0.3373477913074394</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0.3731582319026265</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0.3344010249839847</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0.2924407431133888</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="B110" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C110" s="14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0.3615223707147008</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.3192097617664149</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.3192678675188844</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="B111" s="14" t="n">
+        <v>0.3310344827586207</v>
+      </c>
+      <c r="C111" s="14" t="n">
+        <v>0.3344827586206897</v>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>0.3344827586206897</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0.3410753358577763</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.3413944616893871</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0.3175302024528366</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="B112" s="14" t="n">
+        <v>0.3317972350230414</v>
+      </c>
+      <c r="C112" s="14" t="n">
+        <v>0.3341013824884793</v>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>0.3341013824884793</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>0.3534998553200228</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.3190893562207723</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0.3274107884592049</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="B113" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D113" s="14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0.315780182989113</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.3256972170818929</v>
-      </c>
-      <c r="D92" t="n">
-        <v>0.358522599928994</v>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95">
-      <c r="A95" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 5_Коэффициент степени консенсуса эксперта CDCi</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
+      <c r="B114" s="14" t="n">
+        <v>0.3252510409012981</v>
+      </c>
+      <c r="C114" s="14" t="n">
+        <v>0.337374479549351</v>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>0.337374479549351</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1"/>
+    <row r="116" ht="20" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>7) Коэффициент степени консенсуса эксперта CDC(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="13" t="inlineStr">
         <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 1</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 2</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>Эксперт 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 1</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 2</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>MoSCoW_эксперт 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>0.3134890409332743</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.326473592480278</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.3600373665864477</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="B119" s="14" t="n">
+        <v>0.3125373134328358</v>
+      </c>
+      <c r="C119" s="14" t="n">
+        <v>0.3237313432835821</v>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>0.3637313432835821</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0.331578947368421</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.3094736842105263</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0.3589473684210527</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="B120" s="14" t="n">
+        <v>0.3227120690060136</v>
+      </c>
+      <c r="C120" s="14" t="n">
+        <v>0.3242975019555452</v>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>0.3529904290384411</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0.3204058471596867</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.3045926108678221</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0.3750015419724912</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="B121" s="14" t="n">
+        <v>0.3262031015507754</v>
+      </c>
+      <c r="C121" s="14" t="n">
+        <v>0.3038419209604802</v>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>0.3699549774887444</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>0.3375158375116342</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0.3265842015192002</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0.3358999609691656</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="B122" s="14" t="n">
+        <v>0.3245637210777372</v>
+      </c>
+      <c r="C122" s="14" t="n">
+        <v>0.3235770678182026</v>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>0.3518592111040602</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>0.3376547743966422</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.2993546694648479</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0.36299055613851</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="B123" s="14" t="n">
+        <v>0.320782152697538</v>
+      </c>
+      <c r="C123" s="14" t="n">
+        <v>0.3168091725179983</v>
+      </c>
+      <c r="D123" s="14" t="n">
+        <v>0.3624086747844636</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>0.3438949391415759</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0.3206406149903908</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0.3354644458680333</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="B124" s="14" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="C124" s="14" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>0.3369134224288205</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.3115258570598489</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0.3515607205113306</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="B125" s="14" t="n">
+        <v>0.3186206896551724</v>
+      </c>
+      <c r="C125" s="14" t="n">
+        <v>0.3206896551724138</v>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>0.3606896551724138</v>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0.3246452015146657</v>
-      </c>
-      <c r="C104" t="n">
-        <v>0.3248366770136323</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0.350518121471702</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="B126" s="14" t="n">
+        <v>0.3190783410138248</v>
+      </c>
+      <c r="C126" s="14" t="n">
+        <v>0.3204608294930875</v>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>0.3604608294930876</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0.3320999131920137</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.3114536137324634</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0.356446473075523</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="B127" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C127" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>0.3094681097934678</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.3154183302491357</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0.3751135599573965</v>
-      </c>
-    </row>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 6_Коллективный рейтинг функциональных задач</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="13" t="inlineStr">
+      <c r="B128" s="14" t="n">
+        <v>0.3151506245407788</v>
+      </c>
+      <c r="C128" s="14" t="n">
+        <v>0.3224246877296105</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>0.3624246877296106</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1"/>
+    <row r="130" ht="20" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="15" t="inlineStr">
+        <is>
+          <t>8) Вклад каждого эксперта в коллективную оценку функциональных задач</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
         <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 1*CDCi</t>
-        </is>
-      </c>
-      <c r="C110" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 2*CDCi</t>
-        </is>
-      </c>
-      <c r="D110" s="13" t="inlineStr">
-        <is>
-          <t>Оценка Эксперт 3*CDCi</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 1*CDC(Ei)</t>
+        </is>
+      </c>
+      <c r="C132" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 2*CDC(Ei)</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>Оценка MoSCoW_эксперт 3*CDC(Ei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>4.435869929205832</v>
-      </c>
-      <c r="C111" t="n">
-        <v>4.056434386567454</v>
-      </c>
-      <c r="D111" t="n">
-        <v>4.185434386567454</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="B133" s="14" t="n">
+        <v>7.50089552238806</v>
+      </c>
+      <c r="C133" s="14" t="n">
+        <v>6.960223880597015</v>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>7.820223880597016</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="19" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>2.188421052631579</v>
-      </c>
-      <c r="C112" t="n">
-        <v>2.553157894736842</v>
-      </c>
-      <c r="D112" t="n">
-        <v>2.07292105263158</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="B134" s="14" t="n">
+        <v>4.285616276399861</v>
+      </c>
+      <c r="C134" s="14" t="n">
+        <v>4.378016276399861</v>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>5.328390526335269</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>3.172017886880898</v>
-      </c>
-      <c r="C113" t="n">
-        <v>4.797333621168198</v>
-      </c>
-      <c r="D113" t="n">
-        <v>4.350017886880899</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="B135" s="14" t="n">
+        <v>1.722352376188094</v>
+      </c>
+      <c r="C135" s="14" t="n">
+        <v>2.155758429214607</v>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>2.034752376188094</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="19" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>4.202072177019846</v>
-      </c>
-      <c r="C114" t="n">
-        <v>4.604837241420722</v>
-      </c>
-      <c r="D114" t="n">
-        <v>2.779572177019846</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="B136" s="14" t="n">
+        <v>6.906715984534249</v>
+      </c>
+      <c r="C136" s="14" t="n">
+        <v>6.956906958091357</v>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>6.60791598453425</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>3.629788824763904</v>
-      </c>
-      <c r="C115" t="n">
-        <v>4.714836044071355</v>
-      </c>
-      <c r="D115" t="n">
-        <v>3.312288824763904</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="B137" s="14" t="n">
+        <v>4.234324415607501</v>
+      </c>
+      <c r="C137" s="14" t="n">
+        <v>4.495522158030397</v>
+      </c>
+      <c r="D137" s="14" t="n">
+        <v>4.863524415607502</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="19" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>3.71406534272902</v>
-      </c>
-      <c r="C116" t="n">
-        <v>4.52103267136451</v>
-      </c>
-      <c r="D116" t="n">
-        <v>2.21406534272902</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="B138" s="14" t="n">
+        <v>2.47104</v>
+      </c>
+      <c r="C138" s="14" t="n">
+        <v>2.88684</v>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>3.243240000000001</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>3.638664962231262</v>
-      </c>
-      <c r="C117" t="n">
-        <v>4.39251458454387</v>
-      </c>
-      <c r="D117" t="n">
-        <v>2.909164962231261</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="B139" s="14" t="n">
+        <v>3.364634482758621</v>
+      </c>
+      <c r="C139" s="14" t="n">
+        <v>3.457034482758621</v>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>3.888234482758621</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>4.041832758857589</v>
-      </c>
-      <c r="C118" t="n">
-        <v>4.036095711894381</v>
-      </c>
-      <c r="D118" t="n">
-        <v>3.785595711894381</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="B140" s="14" t="n">
+        <v>5.054200921658985</v>
+      </c>
+      <c r="C140" s="14" t="n">
+        <v>5.146600921658986</v>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>5.789000921658987</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="19" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>3.570074066814147</v>
-      </c>
-      <c r="C119" t="n">
-        <v>4.134546722298452</v>
-      </c>
-      <c r="D119" t="n">
-        <v>3.252574066814147</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="B141" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="14" t="n">
+        <v>0.7623000000000001</v>
+      </c>
+      <c r="D141" s="14" t="n">
+        <v>0.8349000000000001</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="19" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>2.560848608540947</v>
-      </c>
-      <c r="C120" t="n">
-        <v>4.187178334057276</v>
-      </c>
-      <c r="D120" t="n">
-        <v>4.041848608540947</v>
-      </c>
-    </row>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123">
-      <c r="A123" s="13" t="inlineStr">
-        <is>
-          <t>Таблица 7_сортировка коллективного рейтинга функциональных задач по убыванию</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="13" t="inlineStr">
+      <c r="B142" s="14" t="n">
+        <v>4.185200293901543</v>
+      </c>
+      <c r="C142" s="14" t="n">
+        <v>4.601000293901542</v>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>5.171800293901542</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Четкий MoSCoW — итоги (коллективное решение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>1) Сортировка коллективного рейтинга функциональных задач по убыванию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Функциональная задача</t>
         </is>
       </c>
-      <c r="B124" s="13" t="inlineStr">
-        <is>
-          <t>Итоговый коллективный рейтинг функциональной задачи</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Итоговый коллективный рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>12.67773870234074</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="C5" s="14" t="n">
+        <v>22.28134328358209</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>20.47153892715986</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>15.98980276497696</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>13.99202307913499</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>13.95800088170463</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>13.5933709892454</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>10.70990344827586</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>8.601120000000002</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>12.31936939492999</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="C13" s="14" t="n">
+        <v>5.912863181590795</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1.5972</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2) Итоговая приоритизация после учета взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Функциональная задача</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Исходный рейтинг</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Скорректированный рейтинг</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>22.28134328358209</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>22.28134328358209</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>20.47153892715986</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>22.28134328358209</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>13.95800088170463</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>15.98980276497696</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>11.86352418264635</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="C22" s="14" t="n">
+        <v>15.98980276497696</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>15.98980276497696</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1.5972</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>15.98980276497696</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>13.99202307913499</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>13.99202307913499</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>11.65691369359916</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>11.58648159546041</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>10.95719485592675</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="C25" s="14" t="n">
+        <v>13.5933709892454</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>13.5933709892454</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>8.601120000000002</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>10.70990344827586</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>10.94034450900639</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>10.78987555113917</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>FR6</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>10.44916335682255</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>6.814500000000001</v>
+      <c r="C27" s="14" t="n">
+        <v>10.70990344827586</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>10.70990344827586</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>5.912863181590795</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>5.912863181590795</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A81:F81"/>
+  <mergeCells count="2">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
@@ -166,15 +166,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -189,6 +186,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,6 +209,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -565,7 +568,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -580,7 +583,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -602,22 +605,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -658,220 +661,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -896,7 +899,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.5703125" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -911,7 +914,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -933,22 +936,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -989,220 +992,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1227,7 +1230,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.28515625" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
@@ -1242,7 +1245,7 @@
     </row>
     <row r="2"/>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -1264,22 +1267,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1320,220 +1323,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -1558,7 +1561,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2031,7 +2034,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW — расчеты (коллективное решение)</t>
+          <t>Четкий MoSCoW - расчеты (коллективное решение, аналог Hsu 1996)</t>
         </is>
       </c>
     </row>
@@ -2066,10 +2069,10 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2079,10 +2082,10 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2092,23 +2095,23 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="B7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="17" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2138,7 +2141,7 @@
           <t>beta (параметр консенсуса)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2173,162 +2176,162 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="17" t="n">
         <v>21.5</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>13.5</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>15.095</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>7.095000000000001</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="17" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="17" t="n">
         <v>21.28</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>21.5</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>18.78</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="17" t="n">
         <v>13.2</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>14.19</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>13.42</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="17" t="n">
         <v>7.92</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>8.91</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>8.91</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="17" t="n">
         <v>10.56</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>10.78</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>10.78</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="17" t="n">
         <v>15.84</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>16.06</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>16.06</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14" t="n">
+      <c r="B24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="17" t="n">
         <v>1.815</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>1.815</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>14.27</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>14.27</v>
       </c>
     </row>
@@ -2372,13 +2375,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="14" t="n">
+      <c r="B31" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
     </row>
@@ -2388,13 +2391,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="14" t="n">
+      <c r="C32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2404,13 +2407,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14" t="n">
+      <c r="C33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2446,13 +2449,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="14" t="n">
+      <c r="B37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="17" t="n">
         <v>0.9837037037037037</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="17" t="n">
         <v>0.8797615104339186</v>
       </c>
     </row>
@@ -2462,13 +2465,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="17" t="n">
         <v>0.9837037037037037</v>
       </c>
-      <c r="C38" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="14" t="n">
+      <c r="C38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="17" t="n">
         <v>0.8943358728055647</v>
       </c>
     </row>
@@ -2478,13 +2481,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="17" t="n">
         <v>0.8797615104339186</v>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>0.8943358728055647</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2520,13 +2523,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="14" t="n">
+      <c r="B43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="17" t="n">
         <v>0.7441860465116279</v>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="17" t="n">
         <v>0.9600000000000001</v>
       </c>
     </row>
@@ -2536,13 +2539,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="17" t="n">
         <v>0.7441860465116279</v>
       </c>
-      <c r="C44" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="14" t="n">
+      <c r="C44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="17" t="n">
         <v>0.7751937984496123</v>
       </c>
     </row>
@@ -2552,13 +2555,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="17" t="n">
         <v>0.9600000000000001</v>
       </c>
-      <c r="C45" s="14" t="n">
+      <c r="C45" s="17" t="n">
         <v>0.7751937984496123</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D45" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2594,13 +2597,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B49" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="14" t="n">
+      <c r="B49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="17" t="n">
         <v>0.9897674418604652</v>
       </c>
-      <c r="D49" s="14" t="n">
+      <c r="D49" s="17" t="n">
         <v>0.8825187969924813</v>
       </c>
     </row>
@@ -2610,13 +2613,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
+      <c r="B50" s="17" t="n">
         <v>0.9897674418604652</v>
       </c>
-      <c r="C50" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="14" t="n">
+      <c r="C50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="17" t="n">
         <v>0.8734883720930233</v>
       </c>
     </row>
@@ -2626,13 +2629,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B51" s="14" t="n">
+      <c r="B51" s="17" t="n">
         <v>0.8825187969924813</v>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="17" t="n">
         <v>0.8734883720930233</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2668,13 +2671,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="14" t="n">
+      <c r="B55" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="17" t="n">
         <v>0.9302325581395349</v>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="17" t="n">
         <v>0.9836065573770493</v>
       </c>
     </row>
@@ -2684,13 +2687,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="17" t="n">
         <v>0.9302325581395349</v>
       </c>
-      <c r="C56" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="14" t="n">
+      <c r="C56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="17" t="n">
         <v>0.945736434108527</v>
       </c>
     </row>
@@ -2700,13 +2703,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="17" t="n">
         <v>0.9836065573770493</v>
       </c>
-      <c r="C57" s="14" t="n">
+      <c r="C57" s="17" t="n">
         <v>0.945736434108527</v>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D57" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2742,13 +2745,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B61" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="14" t="n">
+      <c r="B61" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="17" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D61" s="17" t="n">
         <v>0.8888888888888888</v>
       </c>
     </row>
@@ -2758,13 +2761,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B62" s="14" t="n">
+      <c r="B62" s="17" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="C62" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="14" t="n">
+      <c r="C62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2774,13 +2777,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B63" s="14" t="n">
+      <c r="B63" s="17" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="C63" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="14" t="n">
+      <c r="C63" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2816,13 +2819,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B67" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" s="14" t="n">
+      <c r="B67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="17" t="n">
         <v>0.9795918367346939</v>
       </c>
-      <c r="D67" s="14" t="n">
+      <c r="D67" s="17" t="n">
         <v>0.9795918367346939</v>
       </c>
     </row>
@@ -2832,13 +2835,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B68" s="14" t="n">
+      <c r="B68" s="17" t="n">
         <v>0.9795918367346939</v>
       </c>
-      <c r="C68" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="14" t="n">
+      <c r="C68" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2848,13 +2851,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B69" s="14" t="n">
+      <c r="B69" s="17" t="n">
         <v>0.9795918367346939</v>
       </c>
-      <c r="C69" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="14" t="n">
+      <c r="C69" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2890,13 +2893,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B73" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" s="14" t="n">
+      <c r="B73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="17" t="n">
         <v>0.9863013698630135</v>
       </c>
-      <c r="D73" s="14" t="n">
+      <c r="D73" s="17" t="n">
         <v>0.9863013698630135</v>
       </c>
     </row>
@@ -2906,13 +2909,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B74" s="14" t="n">
+      <c r="B74" s="17" t="n">
         <v>0.9863013698630135</v>
       </c>
-      <c r="C74" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="14" t="n">
+      <c r="C74" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2922,13 +2925,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B75" s="14" t="n">
+      <c r="B75" s="17" t="n">
         <v>0.9863013698630135</v>
       </c>
-      <c r="C75" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="14" t="n">
+      <c r="C75" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2964,13 +2967,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="14" t="n">
+      <c r="B79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2980,13 +2983,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B80" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="14" t="n">
+      <c r="B80" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2996,13 +2999,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B81" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="14" t="n">
+      <c r="B81" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3038,13 +3041,13 @@
           <t>MoSCoW_эксперт 1</t>
         </is>
       </c>
-      <c r="B85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="14" t="n">
+      <c r="B85" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="17" t="n">
         <v>0.9306236860546603</v>
       </c>
-      <c r="D85" s="14" t="n">
+      <c r="D85" s="17" t="n">
         <v>0.9306236860546603</v>
       </c>
     </row>
@@ -3054,13 +3057,13 @@
           <t>MoSCoW_эксперт 2</t>
         </is>
       </c>
-      <c r="B86" s="14" t="n">
+      <c r="B86" s="17" t="n">
         <v>0.9306236860546603</v>
       </c>
-      <c r="C86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="14" t="n">
+      <c r="C86" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3070,13 +3073,13 @@
           <t>MoSCoW_эксперт 3</t>
         </is>
       </c>
-      <c r="B87" s="14" t="n">
+      <c r="B87" s="17" t="n">
         <v>0.9306236860546603</v>
       </c>
-      <c r="C87" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="14" t="n">
+      <c r="C87" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3111,162 +3114,162 @@
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="19" t="inlineStr">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B91" s="14" t="n">
+      <c r="B91" s="17" t="n">
         <v>0.8958333333333334</v>
       </c>
-      <c r="C91" s="14" t="n">
+      <c r="C91" s="17" t="n">
         <v>0.9479166666666667</v>
       </c>
-      <c r="D91" s="14" t="n">
+      <c r="D91" s="17" t="n">
         <v>0.9479166666666667</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="19" t="inlineStr">
+      <c r="A92" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n">
+      <c r="B92" s="17" t="n">
         <v>0.9317326070688112</v>
       </c>
-      <c r="C92" s="14" t="n">
+      <c r="C92" s="17" t="n">
         <v>0.9390197882546343</v>
       </c>
-      <c r="D92" s="14" t="n">
+      <c r="D92" s="17" t="n">
         <v>0.8870486916197416</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="19" t="inlineStr">
+      <c r="A93" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B93" s="14" t="n">
+      <c r="B93" s="17" t="n">
         <v>0.8520930232558139</v>
       </c>
-      <c r="C93" s="14" t="n">
+      <c r="C93" s="17" t="n">
         <v>0.7596899224806202</v>
       </c>
-      <c r="D93" s="14" t="n">
+      <c r="D93" s="17" t="n">
         <v>0.8675968992248062</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="19" t="inlineStr">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B94" s="14" t="n">
+      <c r="B94" s="17" t="n">
         <v>0.9361431194264732</v>
       </c>
-      <c r="C94" s="14" t="n">
+      <c r="C94" s="17" t="n">
         <v>0.9316279069767442</v>
       </c>
-      <c r="D94" s="14" t="n">
+      <c r="D94" s="17" t="n">
         <v>0.8780035845427523</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="19" t="inlineStr">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B95" s="14" t="n">
+      <c r="B95" s="17" t="n">
         <v>0.9569195577582921</v>
       </c>
-      <c r="C95" s="14" t="n">
+      <c r="C95" s="17" t="n">
         <v>0.9379844961240309</v>
       </c>
-      <c r="D95" s="14" t="n">
+      <c r="D95" s="17" t="n">
         <v>0.9646714957427882</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="19" t="inlineStr">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B96" s="14" t="n">
+      <c r="B96" s="17" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="C96" s="14" t="n">
+      <c r="C96" s="17" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="D96" s="14" t="n">
+      <c r="D96" s="17" t="n">
         <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="19" t="inlineStr">
+      <c r="A97" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B97" s="14" t="n">
+      <c r="B97" s="17" t="n">
         <v>0.9795918367346939</v>
       </c>
-      <c r="C97" s="14" t="n">
+      <c r="C97" s="17" t="n">
         <v>0.9897959183673469</v>
       </c>
-      <c r="D97" s="14" t="n">
+      <c r="D97" s="17" t="n">
         <v>0.9897959183673469</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="19" t="inlineStr">
+      <c r="A98" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B98" s="14" t="n">
+      <c r="B98" s="17" t="n">
         <v>0.9863013698630135</v>
       </c>
-      <c r="C98" s="14" t="n">
+      <c r="C98" s="17" t="n">
         <v>0.9931506849315068</v>
       </c>
-      <c r="D98" s="14" t="n">
+      <c r="D98" s="17" t="n">
         <v>0.9931506849315068</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="19" t="inlineStr">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B99" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="14" t="n">
+      <c r="B99" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="D99" s="14" t="n">
+      <c r="D99" s="17" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="19" t="inlineStr">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B100" s="14" t="n">
+      <c r="B100" s="17" t="n">
         <v>0.9306236860546603</v>
       </c>
-      <c r="C100" s="14" t="n">
+      <c r="C100" s="17" t="n">
         <v>0.9653118430273302</v>
       </c>
-      <c r="D100" s="14" t="n">
+      <c r="D100" s="17" t="n">
         <v>0.9653118430273302</v>
       </c>
     </row>
@@ -3302,162 +3305,162 @@
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B105" s="14" t="n">
+      <c r="B105" s="17" t="n">
         <v>0.3208955223880597</v>
       </c>
-      <c r="C105" s="14" t="n">
+      <c r="C105" s="17" t="n">
         <v>0.3395522388059701</v>
       </c>
-      <c r="D105" s="14" t="n">
+      <c r="D105" s="17" t="n">
         <v>0.3395522388059701</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="19" t="inlineStr">
+      <c r="A106" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
+      <c r="B106" s="17" t="n">
         <v>0.3378534483433561</v>
       </c>
-      <c r="C106" s="14" t="n">
+      <c r="C106" s="17" t="n">
         <v>0.3404958365925754</v>
       </c>
-      <c r="D106" s="14" t="n">
+      <c r="D106" s="17" t="n">
         <v>0.3216507150640686</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="19" t="inlineStr">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B107" s="14" t="n">
+      <c r="B107" s="17" t="n">
         <v>0.343671835917959</v>
       </c>
-      <c r="C107" s="14" t="n">
+      <c r="C107" s="17" t="n">
         <v>0.3064032016008004</v>
       </c>
-      <c r="D107" s="14" t="n">
+      <c r="D107" s="17" t="n">
         <v>0.3499249624812406</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="19" t="inlineStr">
+      <c r="A108" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B108" s="14" t="n">
+      <c r="B108" s="17" t="n">
         <v>0.3409395351295621</v>
       </c>
-      <c r="C108" s="14" t="n">
+      <c r="C108" s="17" t="n">
         <v>0.3392951130303377</v>
       </c>
-      <c r="D108" s="14" t="n">
+      <c r="D108" s="17" t="n">
         <v>0.3197653518401002</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="19" t="inlineStr">
+      <c r="A109" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B109" s="14" t="n">
+      <c r="B109" s="17" t="n">
         <v>0.3346369211625633</v>
       </c>
-      <c r="C109" s="14" t="n">
+      <c r="C109" s="17" t="n">
         <v>0.3280152875299973</v>
       </c>
-      <c r="D109" s="14" t="n">
+      <c r="D109" s="17" t="n">
         <v>0.3373477913074394</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="19" t="inlineStr">
+      <c r="A110" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B110" s="14" t="n">
+      <c r="B110" s="17" t="n">
         <v>0.32</v>
       </c>
-      <c r="C110" s="14" t="n">
+      <c r="C110" s="17" t="n">
         <v>0.34</v>
       </c>
-      <c r="D110" s="14" t="n">
+      <c r="D110" s="17" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="19" t="inlineStr">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B111" s="14" t="n">
+      <c r="B111" s="17" t="n">
         <v>0.3310344827586207</v>
       </c>
-      <c r="C111" s="14" t="n">
+      <c r="C111" s="17" t="n">
         <v>0.3344827586206897</v>
       </c>
-      <c r="D111" s="14" t="n">
+      <c r="D111" s="17" t="n">
         <v>0.3344827586206897</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="19" t="inlineStr">
+      <c r="A112" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B112" s="14" t="n">
+      <c r="B112" s="17" t="n">
         <v>0.3317972350230414</v>
       </c>
-      <c r="C112" s="14" t="n">
+      <c r="C112" s="17" t="n">
         <v>0.3341013824884793</v>
       </c>
-      <c r="D112" s="14" t="n">
+      <c r="D112" s="17" t="n">
         <v>0.3341013824884793</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="19" t="inlineStr">
+      <c r="A113" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B113" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="14" t="n">
+      <c r="B113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="D113" s="14" t="n">
+      <c r="D113" s="17" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="19" t="inlineStr">
+      <c r="A114" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
+      <c r="B114" s="17" t="n">
         <v>0.3252510409012981</v>
       </c>
-      <c r="C114" s="14" t="n">
+      <c r="C114" s="17" t="n">
         <v>0.337374479549351</v>
       </c>
-      <c r="D114" s="14" t="n">
+      <c r="D114" s="17" t="n">
         <v>0.337374479549351</v>
       </c>
     </row>
@@ -3493,162 +3496,162 @@
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="19" t="inlineStr">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B119" s="14" t="n">
+      <c r="B119" s="17" t="n">
         <v>0.3125373134328358</v>
       </c>
-      <c r="C119" s="14" t="n">
+      <c r="C119" s="17" t="n">
         <v>0.3237313432835821</v>
       </c>
-      <c r="D119" s="14" t="n">
+      <c r="D119" s="17" t="n">
         <v>0.3637313432835821</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="19" t="inlineStr">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B120" s="14" t="n">
+      <c r="B120" s="17" t="n">
         <v>0.3227120690060136</v>
       </c>
-      <c r="C120" s="14" t="n">
+      <c r="C120" s="17" t="n">
         <v>0.3242975019555452</v>
       </c>
-      <c r="D120" s="14" t="n">
+      <c r="D120" s="17" t="n">
         <v>0.3529904290384411</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="19" t="inlineStr">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B121" s="14" t="n">
+      <c r="B121" s="17" t="n">
         <v>0.3262031015507754</v>
       </c>
-      <c r="C121" s="14" t="n">
+      <c r="C121" s="17" t="n">
         <v>0.3038419209604802</v>
       </c>
-      <c r="D121" s="14" t="n">
+      <c r="D121" s="17" t="n">
         <v>0.3699549774887444</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="19" t="inlineStr">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B122" s="14" t="n">
+      <c r="B122" s="17" t="n">
         <v>0.3245637210777372</v>
       </c>
-      <c r="C122" s="14" t="n">
+      <c r="C122" s="17" t="n">
         <v>0.3235770678182026</v>
       </c>
-      <c r="D122" s="14" t="n">
+      <c r="D122" s="17" t="n">
         <v>0.3518592111040602</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="19" t="inlineStr">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B123" s="14" t="n">
+      <c r="B123" s="17" t="n">
         <v>0.320782152697538</v>
       </c>
-      <c r="C123" s="14" t="n">
+      <c r="C123" s="17" t="n">
         <v>0.3168091725179983</v>
       </c>
-      <c r="D123" s="14" t="n">
+      <c r="D123" s="17" t="n">
         <v>0.3624086747844636</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="19" t="inlineStr">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B124" s="14" t="n">
+      <c r="B124" s="17" t="n">
         <v>0.312</v>
       </c>
-      <c r="C124" s="14" t="n">
+      <c r="C124" s="17" t="n">
         <v>0.324</v>
       </c>
-      <c r="D124" s="14" t="n">
+      <c r="D124" s="17" t="n">
         <v>0.364</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="19" t="inlineStr">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B125" s="14" t="n">
+      <c r="B125" s="17" t="n">
         <v>0.3186206896551724</v>
       </c>
-      <c r="C125" s="14" t="n">
+      <c r="C125" s="17" t="n">
         <v>0.3206896551724138</v>
       </c>
-      <c r="D125" s="14" t="n">
+      <c r="D125" s="17" t="n">
         <v>0.3606896551724138</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="19" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B126" s="14" t="n">
+      <c r="B126" s="17" t="n">
         <v>0.3190783410138248</v>
       </c>
-      <c r="C126" s="14" t="n">
+      <c r="C126" s="17" t="n">
         <v>0.3204608294930875</v>
       </c>
-      <c r="D126" s="14" t="n">
+      <c r="D126" s="17" t="n">
         <v>0.3604608294930876</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="19" t="inlineStr">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B127" s="14" t="n">
+      <c r="B127" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="C127" s="14" t="n">
+      <c r="C127" s="17" t="n">
         <v>0.42</v>
       </c>
-      <c r="D127" s="14" t="n">
+      <c r="D127" s="17" t="n">
         <v>0.46</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B128" s="14" t="n">
+      <c r="B128" s="17" t="n">
         <v>0.3151506245407788</v>
       </c>
-      <c r="C128" s="14" t="n">
+      <c r="C128" s="17" t="n">
         <v>0.3224246877296105</v>
       </c>
-      <c r="D128" s="14" t="n">
+      <c r="D128" s="17" t="n">
         <v>0.3624246877296106</v>
       </c>
     </row>
@@ -3684,162 +3687,162 @@
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+      <c r="A133" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B133" s="14" t="n">
+      <c r="B133" s="17" t="n">
         <v>7.50089552238806</v>
       </c>
-      <c r="C133" s="14" t="n">
+      <c r="C133" s="17" t="n">
         <v>6.960223880597015</v>
       </c>
-      <c r="D133" s="14" t="n">
+      <c r="D133" s="17" t="n">
         <v>7.820223880597016</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="19" t="inlineStr">
+      <c r="A134" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B134" s="14" t="n">
+      <c r="B134" s="17" t="n">
         <v>4.285616276399861</v>
       </c>
-      <c r="C134" s="14" t="n">
+      <c r="C134" s="17" t="n">
         <v>4.378016276399861</v>
       </c>
-      <c r="D134" s="14" t="n">
+      <c r="D134" s="17" t="n">
         <v>5.328390526335269</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="19" t="inlineStr">
+      <c r="A135" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B135" s="14" t="n">
+      <c r="B135" s="17" t="n">
         <v>1.722352376188094</v>
       </c>
-      <c r="C135" s="14" t="n">
+      <c r="C135" s="17" t="n">
         <v>2.155758429214607</v>
       </c>
-      <c r="D135" s="14" t="n">
+      <c r="D135" s="17" t="n">
         <v>2.034752376188094</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="19" t="inlineStr">
+      <c r="A136" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B136" s="14" t="n">
+      <c r="B136" s="17" t="n">
         <v>6.906715984534249</v>
       </c>
-      <c r="C136" s="14" t="n">
+      <c r="C136" s="17" t="n">
         <v>6.956906958091357</v>
       </c>
-      <c r="D136" s="14" t="n">
+      <c r="D136" s="17" t="n">
         <v>6.60791598453425</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="19" t="inlineStr">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B137" s="14" t="n">
+      <c r="B137" s="17" t="n">
         <v>4.234324415607501</v>
       </c>
-      <c r="C137" s="14" t="n">
+      <c r="C137" s="17" t="n">
         <v>4.495522158030397</v>
       </c>
-      <c r="D137" s="14" t="n">
+      <c r="D137" s="17" t="n">
         <v>4.863524415607502</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="19" t="inlineStr">
+      <c r="A138" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B138" s="14" t="n">
+      <c r="B138" s="17" t="n">
         <v>2.47104</v>
       </c>
-      <c r="C138" s="14" t="n">
+      <c r="C138" s="17" t="n">
         <v>2.88684</v>
       </c>
-      <c r="D138" s="14" t="n">
+      <c r="D138" s="17" t="n">
         <v>3.243240000000001</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="19" t="inlineStr">
+      <c r="A139" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B139" s="14" t="n">
+      <c r="B139" s="17" t="n">
         <v>3.364634482758621</v>
       </c>
-      <c r="C139" s="14" t="n">
+      <c r="C139" s="17" t="n">
         <v>3.457034482758621</v>
       </c>
-      <c r="D139" s="14" t="n">
+      <c r="D139" s="17" t="n">
         <v>3.888234482758621</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="19" t="inlineStr">
+      <c r="A140" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B140" s="14" t="n">
+      <c r="B140" s="17" t="n">
         <v>5.054200921658985</v>
       </c>
-      <c r="C140" s="14" t="n">
+      <c r="C140" s="17" t="n">
         <v>5.146600921658986</v>
       </c>
-      <c r="D140" s="14" t="n">
+      <c r="D140" s="17" t="n">
         <v>5.789000921658987</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="19" t="inlineStr">
+      <c r="A141" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B141" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" s="14" t="n">
+      <c r="B141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="17" t="n">
         <v>0.7623000000000001</v>
       </c>
-      <c r="D141" s="14" t="n">
+      <c r="D141" s="17" t="n">
         <v>0.8349000000000001</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="A142" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B142" s="14" t="n">
+      <c r="B142" s="17" t="n">
         <v>4.185200293901543</v>
       </c>
-      <c r="C142" s="14" t="n">
+      <c r="C142" s="17" t="n">
         <v>4.601000293901542</v>
       </c>
-      <c r="D142" s="14" t="n">
+      <c r="D142" s="17" t="n">
         <v>5.171800293901542</v>
       </c>
     </row>
@@ -3866,7 +3869,7 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
@@ -3875,7 +3878,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW — итоги (коллективное решение)</t>
+          <t>Четкий MoSCoW - итоги (коллективное решение, аналог Hsu 1996)</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3911,12 @@
       <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>22.28134328358209</v>
       </c>
     </row>
@@ -3921,12 +3924,12 @@
       <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>20.47153892715986</v>
       </c>
     </row>
@@ -3934,12 +3937,12 @@
       <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>15.98980276497696</v>
       </c>
     </row>
@@ -3947,12 +3950,12 @@
       <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="17" t="n">
         <v>13.99202307913499</v>
       </c>
     </row>
@@ -3960,12 +3963,12 @@
       <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="17" t="n">
         <v>13.95800088170463</v>
       </c>
     </row>
@@ -3973,12 +3976,12 @@
       <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="17" t="n">
         <v>13.5933709892454</v>
       </c>
     </row>
@@ -3986,12 +3989,12 @@
       <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>10.70990344827586</v>
       </c>
     </row>
@@ -3999,12 +4002,12 @@
       <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>8.601120000000002</v>
       </c>
     </row>
@@ -4012,12 +4015,12 @@
       <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>5.912863181590795</v>
       </c>
     </row>
@@ -4025,12 +4028,12 @@
       <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>1.5972</v>
       </c>
     </row>
@@ -4069,15 +4072,15 @@
       <c r="A19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>22.28134328358209</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>22.28134328358209</v>
       </c>
     </row>
@@ -4085,15 +4088,15 @@
       <c r="A20" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>20.47153892715986</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>22.28134328358209</v>
       </c>
     </row>
@@ -4101,15 +4104,15 @@
       <c r="A21" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>13.95800088170463</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>15.98980276497696</v>
       </c>
     </row>
@@ -4117,15 +4120,15 @@
       <c r="A22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>15.98980276497696</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>15.98980276497696</v>
       </c>
     </row>
@@ -4133,15 +4136,15 @@
       <c r="A23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>1.5972</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>15.98980276497696</v>
       </c>
     </row>
@@ -4149,15 +4152,15 @@
       <c r="A24" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>13.99202307913499</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>13.99202307913499</v>
       </c>
     </row>
@@ -4165,15 +4168,15 @@
       <c r="A25" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>13.5933709892454</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>13.5933709892454</v>
       </c>
     </row>
@@ -4181,15 +4184,15 @@
       <c r="A26" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>8.601120000000002</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>10.70990344827586</v>
       </c>
     </row>
@@ -4197,15 +4200,15 @@
       <c r="A27" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>10.70990344827586</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>10.70990344827586</v>
       </c>
     </row>
@@ -4213,15 +4216,15 @@
       <c r="A28" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>5.912863181590795</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>5.912863181590795</v>
       </c>
     </row>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_Hsu 1996.xlsx
@@ -2119,7 +2119,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>2) Параметры алгоритма</t>
+          <t>2) Гиперпараметры модели</t>
         </is>
       </c>
     </row>
